--- a/news_daily/2026-09-04.xlsx
+++ b/news_daily/2026-09-04.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$60</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
@@ -2007,13 +2007,17 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -2066,7 +2070,11 @@
         </is>
       </c>
       <c r="AA8" s="4" t="inlineStr"/>
-      <c r="AB8" s="4" t="inlineStr"/>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>a107611c11f14a668755c0c26c9540a7</t>
+        </is>
+      </c>
       <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>b3ab7fad919e0e7e446f8c5f</t>
@@ -2087,7 +2095,11 @@
       <c r="AL8" s="4" t="inlineStr"/>
       <c r="AM8" s="4" t="inlineStr"/>
       <c r="AN8" s="4" t="inlineStr"/>
-      <c r="AO8" s="4" t="inlineStr"/>
+      <c r="AO8" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="4" t="inlineStr"/>
       <c r="AQ8" s="4" t="inlineStr"/>
       <c r="AR8" s="4" t="inlineStr"/>
@@ -2125,8 +2137,16 @@
       <c r="BH8" s="4" t="inlineStr"/>
       <c r="BI8" s="4" t="inlineStr"/>
       <c r="BJ8" s="4" t="inlineStr"/>
-      <c r="BK8" s="4" t="inlineStr"/>
-      <c r="BL8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2577,13 +2597,17 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -2636,7 +2660,11 @@
         </is>
       </c>
       <c r="AA11" s="4" t="inlineStr"/>
-      <c r="AB11" s="4" t="inlineStr"/>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t>f23d6cd114bb4d939521cad9f5f958d3</t>
+        </is>
+      </c>
       <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>fd532b02299d31627f667033</t>
@@ -2657,7 +2685,11 @@
       <c r="AL11" s="4" t="inlineStr"/>
       <c r="AM11" s="4" t="inlineStr"/>
       <c r="AN11" s="4" t="inlineStr"/>
-      <c r="AO11" s="4" t="inlineStr"/>
+      <c r="AO11" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="4" t="inlineStr"/>
       <c r="AQ11" s="4" t="inlineStr"/>
       <c r="AR11" s="4" t="inlineStr"/>
@@ -2703,8 +2735,16 @@
       <c r="BH11" s="4" t="inlineStr"/>
       <c r="BI11" s="4" t="inlineStr"/>
       <c r="BJ11" s="4" t="inlineStr"/>
-      <c r="BK11" s="4" t="inlineStr"/>
-      <c r="BL11" s="4" t="inlineStr"/>
+      <c r="BK11" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -4069,13 +4109,17 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -4128,7 +4172,11 @@
         </is>
       </c>
       <c r="AA19" s="4" t="inlineStr"/>
-      <c r="AB19" s="4" t="inlineStr"/>
+      <c r="AB19" s="4" t="inlineStr">
+        <is>
+          <t>897f74cd711049b9976b923e6f0aaa30</t>
+        </is>
+      </c>
       <c r="AC19" s="4" t="inlineStr">
         <is>
           <t>f63fb512633513e2baee5996</t>
@@ -4149,7 +4197,11 @@
       <c r="AL19" s="4" t="inlineStr"/>
       <c r="AM19" s="4" t="inlineStr"/>
       <c r="AN19" s="4" t="inlineStr"/>
-      <c r="AO19" s="4" t="inlineStr"/>
+      <c r="AO19" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP19" s="4" t="inlineStr"/>
       <c r="AQ19" s="4" t="inlineStr"/>
       <c r="AR19" s="4" t="inlineStr"/>
@@ -4195,8 +4247,16 @@
       <c r="BH19" s="4" t="inlineStr"/>
       <c r="BI19" s="4" t="inlineStr"/>
       <c r="BJ19" s="4" t="inlineStr"/>
-      <c r="BK19" s="4" t="inlineStr"/>
-      <c r="BL19" s="4" t="inlineStr"/>
+      <c r="BK19" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4725,182 +4785,206 @@
       <c r="BL22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>TSN</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Tyson Foods, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>2026-09-04T05:51:19+08:00</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Alouettes host Lions with another chance to clinch playoff spot on TSN</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr"/>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0.162</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQN05KSG1TN1Nsckc2b3dQSi11TG80Q2MxajQ3cU5BMVV2eWJBYWNpVjJGc1lTRnZxcnZWVE83SjBpOTBjQ09JUEczenVYUXNNMXQ5aVZKZHlVZ0dGMHk5cjFxOWFTOTNWdUhMQmhXOW5FUS1yRlVUZnk1VUdHNHUyWEhxUzd6Z0lxc2V4cWp0SHByUmNxRWFaVDVUUHlpZTBXbG1Rdg?oc=5</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>TSN</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>Alouettes 主場迎戰 Lions，再次有機會在 TSN 上鎖定季後賽席位</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>layoff</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>317ec4a7bf804a2a8e8e566334cd01d2</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>bf62a5c30cd01f9ee4678ab7</t>
+        </is>
+      </c>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>f83c83a5d25f3d395cb68e4a</t>
+        </is>
+      </c>
+      <c r="AE23" s="2" t="inlineStr"/>
+      <c r="AF23" s="2" t="inlineStr"/>
+      <c r="AG23" s="2" t="inlineStr"/>
+      <c r="AH23" s="2" t="inlineStr"/>
+      <c r="AI23" s="2" t="inlineStr"/>
+      <c r="AJ23" s="2" t="inlineStr"/>
+      <c r="AK23" s="2" t="inlineStr"/>
+      <c r="AL23" s="2" t="inlineStr"/>
+      <c r="AM23" s="2" t="inlineStr"/>
+      <c r="AN23" s="2" t="inlineStr"/>
+      <c r="AO23" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O23" s="4" t="inlineStr">
-        <is>
-          <t>0.162</t>
-        </is>
-      </c>
-      <c r="P23" s="4" t="inlineStr"/>
-      <c r="Q23" s="4" t="inlineStr"/>
-      <c r="R23" s="4" t="inlineStr"/>
-      <c r="S23" s="4" t="inlineStr"/>
-      <c r="T23" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U23" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQN05KSG1TN1Nsckc2b3dQSi11TG80Q2MxajQ3cU5BMVV2eWJBYWNpVjJGc1lTRnZxcnZWVE83SjBpOTBjQ09JUEczenVYUXNNMXQ5aVZKZHlVZ0dGMHk5cjFxOWFTOTNWdUhMQmhXOW5FUS1yRlVUZnk1VUdHNHUyWEhxUzd6Z0lxc2V4cWp0SHByUmNxRWFaVDVUUHlpZTBXbG1Rdg?oc=5</t>
-        </is>
-      </c>
-      <c r="V23" s="4" t="inlineStr">
+      <c r="AP23" s="2" t="inlineStr"/>
+      <c r="AQ23" s="2" t="inlineStr"/>
+      <c r="AR23" s="2" t="inlineStr"/>
+      <c r="AS23" s="2" t="inlineStr"/>
+      <c r="AT23" s="2" t="inlineStr"/>
+      <c r="AU23" s="2" t="inlineStr"/>
+      <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" s="2" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX23" s="2" t="inlineStr"/>
+      <c r="AY23" s="2" t="inlineStr"/>
+      <c r="AZ23" s="2" t="inlineStr"/>
+      <c r="BA23" s="2" t="inlineStr"/>
+      <c r="BB23" s="2" t="inlineStr">
         <is>
           <t>TSN</t>
         </is>
       </c>
-      <c r="W23" s="4" t="inlineStr">
-        <is>
-          <t>Alouettes 主場迎戰 Lions，再次有機會在 TSN 上鎖定季後賽席位</t>
-        </is>
-      </c>
-      <c r="X23" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y23" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z23" s="4" t="inlineStr">
-        <is>
-          <t>layoff</t>
-        </is>
-      </c>
-      <c r="AA23" s="4" t="inlineStr"/>
-      <c r="AB23" s="4" t="inlineStr"/>
-      <c r="AC23" s="4" t="inlineStr">
-        <is>
-          <t>bf62a5c30cd01f9ee4678ab7</t>
-        </is>
-      </c>
-      <c r="AD23" s="4" t="inlineStr">
-        <is>
-          <t>f83c83a5d25f3d395cb68e4a</t>
-        </is>
-      </c>
-      <c r="AE23" s="4" t="inlineStr"/>
-      <c r="AF23" s="4" t="inlineStr"/>
-      <c r="AG23" s="4" t="inlineStr"/>
-      <c r="AH23" s="4" t="inlineStr"/>
-      <c r="AI23" s="4" t="inlineStr"/>
-      <c r="AJ23" s="4" t="inlineStr"/>
-      <c r="AK23" s="4" t="inlineStr"/>
-      <c r="AL23" s="4" t="inlineStr"/>
-      <c r="AM23" s="4" t="inlineStr"/>
-      <c r="AN23" s="4" t="inlineStr"/>
-      <c r="AO23" s="4" t="inlineStr"/>
-      <c r="AP23" s="4" t="inlineStr"/>
-      <c r="AQ23" s="4" t="inlineStr"/>
-      <c r="AR23" s="4" t="inlineStr"/>
-      <c r="AS23" s="4" t="inlineStr"/>
-      <c r="AT23" s="4" t="inlineStr"/>
-      <c r="AU23" s="4" t="inlineStr"/>
-      <c r="AV23" s="4" t="inlineStr"/>
-      <c r="AW23" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX23" s="4" t="inlineStr"/>
-      <c r="AY23" s="4" t="inlineStr"/>
-      <c r="AZ23" s="4" t="inlineStr"/>
-      <c r="BA23" s="4" t="inlineStr"/>
-      <c r="BB23" s="4" t="inlineStr">
-        <is>
-          <t>TSN</t>
-        </is>
-      </c>
-      <c r="BC23" s="4" t="inlineStr">
+      <c r="BC23" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD23" s="4" t="inlineStr"/>
-      <c r="BE23" s="4" t="inlineStr">
+      <c r="BD23" s="2" t="inlineStr"/>
+      <c r="BE23" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF23" s="4" t="inlineStr">
+      <c r="BF23" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG23" s="4" t="inlineStr">
+      <c r="BG23" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH23" s="4" t="inlineStr"/>
-      <c r="BI23" s="4" t="inlineStr"/>
-      <c r="BJ23" s="4" t="inlineStr"/>
-      <c r="BK23" s="4" t="inlineStr"/>
-      <c r="BL23" s="4" t="inlineStr"/>
+      <c r="BH23" s="2" t="inlineStr"/>
+      <c r="BI23" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ23" s="2" t="inlineStr"/>
+      <c r="BK23" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -7543,13 +7627,17 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L38" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -7602,7 +7690,11 @@
         </is>
       </c>
       <c r="AA38" s="4" t="inlineStr"/>
-      <c r="AB38" s="4" t="inlineStr"/>
+      <c r="AB38" s="4" t="inlineStr">
+        <is>
+          <t>4b29cf62a8f745eab64d70327b09097b</t>
+        </is>
+      </c>
       <c r="AC38" s="4" t="inlineStr">
         <is>
           <t>aa553e018d73a9b0841471ee</t>
@@ -7623,7 +7715,11 @@
       <c r="AL38" s="4" t="inlineStr"/>
       <c r="AM38" s="4" t="inlineStr"/>
       <c r="AN38" s="4" t="inlineStr"/>
-      <c r="AO38" s="4" t="inlineStr"/>
+      <c r="AO38" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP38" s="4" t="inlineStr"/>
       <c r="AQ38" s="4" t="inlineStr"/>
       <c r="AR38" s="4" t="inlineStr"/>
@@ -7661,8 +7757,16 @@
       <c r="BH38" s="4" t="inlineStr"/>
       <c r="BI38" s="4" t="inlineStr"/>
       <c r="BJ38" s="4" t="inlineStr"/>
-      <c r="BK38" s="4" t="inlineStr"/>
-      <c r="BL38" s="4" t="inlineStr"/>
+      <c r="BK38" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -10887,182 +10991,206 @@
       <c r="BL55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UBER</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Uber Technologies, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>2026-09-04T01:02:00+08:00</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>I was laid off from Uber again. As a boomerang employee, my worst fear came true.</t>
         </is>
       </c>
-      <c r="G56" s="4" t="inlineStr"/>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I56" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L56" s="4" t="inlineStr"/>
-      <c r="M56" s="4" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>'-0.762</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQV1lSRXpvTW9FUm9jVkw4XzZOS0ZBYndfR0VlUVE1eTBXVHYtUjI0aVgtYWNHQ3o0eEtaR0c5Tnl6T0lJYjNYUkpKbXk2RG5MeXdvaS0yRXNpWC1VVk1lVDVpRkoxb25xVHRfeGRCdUVMb2l1cHNPZ1kwVjF6SEVqU2R6RGlyRnBzTTdCYQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>Business Insider</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>我又被 Uber 解雇了。身為迴力鏢員工，我最擔心的事情成真了。</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>laid off</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr"/>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>07a726b47c83481395bdb1691d716b9a</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>a767a2e2968e7ba2894a38b9</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>9a3859e34af691eaf36ef1aa</t>
+        </is>
+      </c>
+      <c r="AE56" s="2" t="inlineStr"/>
+      <c r="AF56" s="2" t="inlineStr"/>
+      <c r="AG56" s="2" t="inlineStr"/>
+      <c r="AH56" s="2" t="inlineStr"/>
+      <c r="AI56" s="2" t="inlineStr"/>
+      <c r="AJ56" s="2" t="inlineStr"/>
+      <c r="AK56" s="2" t="inlineStr"/>
+      <c r="AL56" s="2" t="inlineStr"/>
+      <c r="AM56" s="2" t="inlineStr"/>
+      <c r="AN56" s="2" t="inlineStr"/>
+      <c r="AO56" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N56" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O56" s="4" t="inlineStr">
-        <is>
-          <t>'-0.762</t>
-        </is>
-      </c>
-      <c r="P56" s="4" t="inlineStr"/>
-      <c r="Q56" s="4" t="inlineStr"/>
-      <c r="R56" s="4" t="inlineStr"/>
-      <c r="S56" s="4" t="inlineStr"/>
-      <c r="T56" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U56" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQV1lSRXpvTW9FUm9jVkw4XzZOS0ZBYndfR0VlUVE1eTBXVHYtUjI0aVgtYWNHQ3o0eEtaR0c5Tnl6T0lJYjNYUkpKbXk2RG5MeXdvaS0yRXNpWC1VVk1lVDVpRkoxb25xVHRfeGRCdUVMb2l1cHNPZ1kwVjF6SEVqU2R6RGlyRnBzTTdCYQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V56" s="4" t="inlineStr">
-        <is>
-          <t>Business Insider</t>
-        </is>
-      </c>
-      <c r="W56" s="4" t="inlineStr">
-        <is>
-          <t>我又被 Uber 解雇了。身為迴力鏢員工，我最擔心的事情成真了。</t>
-        </is>
-      </c>
-      <c r="X56" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y56" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z56" s="4" t="inlineStr">
-        <is>
-          <t>laid off</t>
-        </is>
-      </c>
-      <c r="AA56" s="4" t="inlineStr"/>
-      <c r="AB56" s="4" t="inlineStr"/>
-      <c r="AC56" s="4" t="inlineStr">
-        <is>
-          <t>a767a2e2968e7ba2894a38b9</t>
-        </is>
-      </c>
-      <c r="AD56" s="4" t="inlineStr">
-        <is>
-          <t>9a3859e34af691eaf36ef1aa</t>
-        </is>
-      </c>
-      <c r="AE56" s="4" t="inlineStr"/>
-      <c r="AF56" s="4" t="inlineStr"/>
-      <c r="AG56" s="4" t="inlineStr"/>
-      <c r="AH56" s="4" t="inlineStr"/>
-      <c r="AI56" s="4" t="inlineStr"/>
-      <c r="AJ56" s="4" t="inlineStr"/>
-      <c r="AK56" s="4" t="inlineStr"/>
-      <c r="AL56" s="4" t="inlineStr"/>
-      <c r="AM56" s="4" t="inlineStr"/>
-      <c r="AN56" s="4" t="inlineStr"/>
-      <c r="AO56" s="4" t="inlineStr"/>
-      <c r="AP56" s="4" t="inlineStr"/>
-      <c r="AQ56" s="4" t="inlineStr"/>
-      <c r="AR56" s="4" t="inlineStr"/>
-      <c r="AS56" s="4" t="inlineStr"/>
-      <c r="AT56" s="4" t="inlineStr"/>
-      <c r="AU56" s="4" t="inlineStr"/>
-      <c r="AV56" s="4" t="inlineStr"/>
-      <c r="AW56" s="4" t="inlineStr">
+      <c r="AP56" s="2" t="inlineStr"/>
+      <c r="AQ56" s="2" t="inlineStr"/>
+      <c r="AR56" s="2" t="inlineStr"/>
+      <c r="AS56" s="2" t="inlineStr"/>
+      <c r="AT56" s="2" t="inlineStr"/>
+      <c r="AU56" s="2" t="inlineStr"/>
+      <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX56" s="4" t="inlineStr"/>
-      <c r="AY56" s="4" t="inlineStr"/>
-      <c r="AZ56" s="4" t="inlineStr"/>
-      <c r="BA56" s="4" t="inlineStr"/>
-      <c r="BB56" s="4" t="inlineStr">
+      <c r="AX56" s="2" t="inlineStr"/>
+      <c r="AY56" s="2" t="inlineStr"/>
+      <c r="AZ56" s="2" t="inlineStr"/>
+      <c r="BA56" s="2" t="inlineStr"/>
+      <c r="BB56" s="2" t="inlineStr">
         <is>
           <t>UBER</t>
         </is>
       </c>
-      <c r="BC56" s="4" t="inlineStr">
+      <c r="BC56" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD56" s="4" t="inlineStr"/>
-      <c r="BE56" s="4" t="inlineStr">
+      <c r="BD56" s="2" t="inlineStr"/>
+      <c r="BE56" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF56" s="4" t="inlineStr">
+      <c r="BF56" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG56" s="4" t="inlineStr">
+      <c r="BG56" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH56" s="4" t="inlineStr"/>
-      <c r="BI56" s="4" t="inlineStr"/>
-      <c r="BJ56" s="4" t="inlineStr"/>
-      <c r="BK56" s="4" t="inlineStr"/>
-      <c r="BL56" s="4" t="inlineStr"/>
+      <c r="BH56" s="2" t="inlineStr"/>
+      <c r="BI56" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ56" s="2" t="inlineStr"/>
+      <c r="BK56" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -11113,13 +11241,17 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L57" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -11172,7 +11304,11 @@
         </is>
       </c>
       <c r="AA57" s="4" t="inlineStr"/>
-      <c r="AB57" s="4" t="inlineStr"/>
+      <c r="AB57" s="4" t="inlineStr">
+        <is>
+          <t>95d008d6c03f444a82c3f94ddd3b5aab</t>
+        </is>
+      </c>
       <c r="AC57" s="4" t="inlineStr">
         <is>
           <t>55985b65cf2ed55e27be34dd</t>
@@ -11193,7 +11329,11 @@
       <c r="AL57" s="4" t="inlineStr"/>
       <c r="AM57" s="4" t="inlineStr"/>
       <c r="AN57" s="4" t="inlineStr"/>
-      <c r="AO57" s="4" t="inlineStr"/>
+      <c r="AO57" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP57" s="4" t="inlineStr"/>
       <c r="AQ57" s="4" t="inlineStr"/>
       <c r="AR57" s="4" t="inlineStr"/>
@@ -11239,8 +11379,16 @@
       <c r="BH57" s="4" t="inlineStr"/>
       <c r="BI57" s="4" t="inlineStr"/>
       <c r="BJ57" s="4" t="inlineStr"/>
-      <c r="BK57" s="4" t="inlineStr"/>
-      <c r="BL57" s="4" t="inlineStr"/>
+      <c r="BK57" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL57" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11800,7 +11948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL18"/>
+  <dimension ref="A1:BL16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12818,13 +12966,17 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -12877,7 +13029,11 @@
         </is>
       </c>
       <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="inlineStr">
+        <is>
+          <t>a107611c11f14a668755c0c26c9540a7</t>
+        </is>
+      </c>
       <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>b3ab7fad919e0e7e446f8c5f</t>
@@ -12898,7 +13054,11 @@
       <c r="AL5" s="4" t="inlineStr"/>
       <c r="AM5" s="4" t="inlineStr"/>
       <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr"/>
+      <c r="AO5" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="4" t="inlineStr"/>
       <c r="AQ5" s="4" t="inlineStr"/>
       <c r="AR5" s="4" t="inlineStr"/>
@@ -12936,8 +13096,16 @@
       <c r="BH5" s="4" t="inlineStr"/>
       <c r="BI5" s="4" t="inlineStr"/>
       <c r="BJ5" s="4" t="inlineStr"/>
-      <c r="BK5" s="4" t="inlineStr"/>
-      <c r="BL5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -13186,13 +13354,17 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -13245,7 +13417,11 @@
         </is>
       </c>
       <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="inlineStr"/>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>f23d6cd114bb4d939521cad9f5f958d3</t>
+        </is>
+      </c>
       <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>fd532b02299d31627f667033</t>
@@ -13266,7 +13442,11 @@
       <c r="AL7" s="4" t="inlineStr"/>
       <c r="AM7" s="4" t="inlineStr"/>
       <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="inlineStr"/>
+      <c r="AO7" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="4" t="inlineStr"/>
       <c r="AQ7" s="4" t="inlineStr"/>
       <c r="AR7" s="4" t="inlineStr"/>
@@ -13312,8 +13492,16 @@
       <c r="BH7" s="4" t="inlineStr"/>
       <c r="BI7" s="4" t="inlineStr"/>
       <c r="BJ7" s="4" t="inlineStr"/>
-      <c r="BK7" s="4" t="inlineStr"/>
-      <c r="BL7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -13554,13 +13742,17 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -13613,7 +13805,11 @@
         </is>
       </c>
       <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>897f74cd711049b9976b923e6f0aaa30</t>
+        </is>
+      </c>
       <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>f63fb512633513e2baee5996</t>
@@ -13634,7 +13830,11 @@
       <c r="AL9" s="4" t="inlineStr"/>
       <c r="AM9" s="4" t="inlineStr"/>
       <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="inlineStr"/>
+      <c r="AO9" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="4" t="inlineStr"/>
       <c r="AQ9" s="4" t="inlineStr"/>
       <c r="AR9" s="4" t="inlineStr"/>
@@ -13680,546 +13880,586 @@
       <c r="BH9" s="4" t="inlineStr"/>
       <c r="BI9" s="4" t="inlineStr"/>
       <c r="BJ9" s="4" t="inlineStr"/>
-      <c r="BK9" s="4" t="inlineStr"/>
-      <c r="BL9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>TSN</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Tyson Foods, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04T05:51:19+08:00</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Alouettes host Lions with another chance to clinch playoff spot on TSN</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Pentair</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:57:00+08:00</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Pentair plc (PNR) Notice of October 2, 2026 Application Deadline for Class Action Lawsuit</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>'-0.142</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOM1UyUFhsenlXTXN1WlZ0TGNORG0tcThNQWFwMmxsU3BlUzRlRmh3Z0diTnVFR0xTZkN1VzVHWFZwNDV1aTA1TTc3NHBwd1ZtV254VUxJR2tGaldvYVZ3a2ZYcG9KWlFzdzVKOElwSDhxdUlJeWxUTlFBbWZqaEYteFJxNXgxaDROQUp2eGNEbHlNQ1ZuMS1JVHo2NmM0NXhScmdWQ1dQMG01T0VuNGdCYUtqc3RBYjR0dE9nOTBqR25vdS1zUll2aFBHRW02VlRvaFdvdUFQRHNOQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>Pentair plc (PNR) 關於 2026 年 10 月 2 日集體訴訟申請截止日期的通知</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>99636fa610ad48d08b6762190fa10e84</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>4309789bd13b14ad9ad6fe88</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr">
+        <is>
+          <t>ee6678be577c258f20468ef6</t>
+        </is>
+      </c>
+      <c r="AE10" s="3" t="inlineStr"/>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr"/>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr"/>
+      <c r="AM10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t>0.162</t>
-        </is>
-      </c>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr"/>
-      <c r="R10" s="4" t="inlineStr"/>
-      <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQN05KSG1TN1Nsckc2b3dQSi11TG80Q2MxajQ3cU5BMVV2eWJBYWNpVjJGc1lTRnZxcnZWVE83SjBpOTBjQ09JUEczenVYUXNNMXQ5aVZKZHlVZ0dGMHk5cjFxOWFTOTNWdUhMQmhXOW5FUS1yRlVUZnk1VUdHNHUyWEhxUzd6Z0lxc2V4cWp0SHByUmNxRWFaVDVUUHlpZTBXbG1Rdg?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="inlineStr">
-        <is>
-          <t>TSN</t>
-        </is>
-      </c>
-      <c r="W10" s="4" t="inlineStr">
-        <is>
-          <t>Alouettes 主場迎戰 Lions，再次有機會在 TSN 上鎖定季後賽席位</t>
-        </is>
-      </c>
-      <c r="X10" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y10" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z10" s="4" t="inlineStr">
-        <is>
-          <t>layoff</t>
-        </is>
-      </c>
-      <c r="AA10" s="4" t="inlineStr"/>
-      <c r="AB10" s="4" t="inlineStr"/>
-      <c r="AC10" s="4" t="inlineStr">
-        <is>
-          <t>bf62a5c30cd01f9ee4678ab7</t>
-        </is>
-      </c>
-      <c r="AD10" s="4" t="inlineStr">
-        <is>
-          <t>f83c83a5d25f3d395cb68e4a</t>
-        </is>
-      </c>
-      <c r="AE10" s="4" t="inlineStr"/>
-      <c r="AF10" s="4" t="inlineStr"/>
-      <c r="AG10" s="4" t="inlineStr"/>
-      <c r="AH10" s="4" t="inlineStr"/>
-      <c r="AI10" s="4" t="inlineStr"/>
-      <c r="AJ10" s="4" t="inlineStr"/>
-      <c r="AK10" s="4" t="inlineStr"/>
-      <c r="AL10" s="4" t="inlineStr"/>
-      <c r="AM10" s="4" t="inlineStr"/>
-      <c r="AN10" s="4" t="inlineStr"/>
-      <c r="AO10" s="4" t="inlineStr"/>
-      <c r="AP10" s="4" t="inlineStr"/>
-      <c r="AQ10" s="4" t="inlineStr"/>
-      <c r="AR10" s="4" t="inlineStr"/>
-      <c r="AS10" s="4" t="inlineStr"/>
-      <c r="AT10" s="4" t="inlineStr"/>
-      <c r="AU10" s="4" t="inlineStr"/>
-      <c r="AV10" s="4" t="inlineStr"/>
-      <c r="AW10" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX10" s="4" t="inlineStr"/>
-      <c r="AY10" s="4" t="inlineStr"/>
-      <c r="AZ10" s="4" t="inlineStr"/>
-      <c r="BA10" s="4" t="inlineStr"/>
-      <c r="BB10" s="4" t="inlineStr">
-        <is>
-          <t>TSN</t>
-        </is>
-      </c>
-      <c r="BC10" s="4" t="inlineStr">
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr"/>
+      <c r="AS10" s="3" t="inlineStr"/>
+      <c r="AT10" s="3" t="inlineStr"/>
+      <c r="AU10" s="3" t="inlineStr"/>
+      <c r="AV10" s="3" t="inlineStr"/>
+      <c r="AW10" s="3" t="inlineStr"/>
+      <c r="AX10" s="3" t="inlineStr"/>
+      <c r="AY10" s="3" t="inlineStr"/>
+      <c r="AZ10" s="3" t="inlineStr"/>
+      <c r="BA10" s="3" t="inlineStr"/>
+      <c r="BB10" s="3" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="BC10" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD10" s="4" t="inlineStr"/>
-      <c r="BE10" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF10" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG10" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH10" s="4" t="inlineStr"/>
-      <c r="BI10" s="4" t="inlineStr"/>
-      <c r="BJ10" s="4" t="inlineStr"/>
-      <c r="BK10" s="4" t="inlineStr"/>
-      <c r="BL10" s="4" t="inlineStr"/>
+      <c r="BD10" s="3" t="inlineStr"/>
+      <c r="BE10" s="3" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF10" s="3" t="inlineStr"/>
+      <c r="BG10" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Pentair</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04T04:57:00+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Pentair plc (PNR) Notice of October 2, 2026 Application Deadline for Class Action Lawsuit</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>HPE</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04T04:10:52+08:00</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>AI demand is 'exceptional,' but the supply chain is not: HPE CEO</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>供應鏈中斷</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>'-0.142</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>0.246</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr"/>
+      <c r="Q11" s="4" t="inlineStr"/>
+      <c r="R11" s="4" t="inlineStr"/>
+      <c r="S11" s="4" t="inlineStr"/>
+      <c r="T11" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOM1UyUFhsenlXTXN1WlZ0TGNORG0tcThNQWFwMmxsU3BlUzRlRmh3Z0diTnVFR0xTZkN1VzVHWFZwNDV1aTA1TTc3NHBwd1ZtV254VUxJR2tGaldvYVZ3a2ZYcG9KWlFzdzVKOElwSDhxdUlJeWxUTlFBbWZqaEYteFJxNXgxaDROQUp2eGNEbHlNQ1ZuMS1JVHo2NmM0NXhScmdWQ1dQMG01T0VuNGdCYUtqc3RBYjR0dE9nOTBqR25vdS1zUll2aFBHRW02VlRvaFdvdUFQRHNOQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t>PR Newswire</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t>Pentair plc (PNR) 關於 2026 年 10 月 2 日集體訴訟申請截止日期的通知</t>
-        </is>
-      </c>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA11" s="3" t="inlineStr"/>
-      <c r="AB11" s="3" t="inlineStr">
-        <is>
-          <t>99636fa610ad48d08b6762190fa10e84</t>
-        </is>
-      </c>
-      <c r="AC11" s="3" t="inlineStr">
-        <is>
-          <t>4309789bd13b14ad9ad6fe88</t>
-        </is>
-      </c>
-      <c r="AD11" s="3" t="inlineStr">
-        <is>
-          <t>ee6678be577c258f20468ef6</t>
-        </is>
-      </c>
-      <c r="AE11" s="3" t="inlineStr"/>
-      <c r="AF11" s="3" t="inlineStr"/>
-      <c r="AG11" s="3" t="inlineStr"/>
-      <c r="AH11" s="3" t="inlineStr"/>
-      <c r="AI11" s="3" t="inlineStr"/>
-      <c r="AJ11" s="3" t="inlineStr"/>
-      <c r="AK11" s="3" t="inlineStr"/>
-      <c r="AL11" s="3" t="inlineStr"/>
-      <c r="AM11" s="3" t="inlineStr"/>
-      <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr">
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPZnp0VmlSaS00dG1nOFlHREZRTDFNcDJwMjdvY2pTdGZPRDUtRlE5VjhzSXQwMFZfaTgwdE5xcG10TTBxejhrQ25MdXdnMFoySEpibzIxX0xPX05rNTIydFlOOUMxNmRfVkR4MWNESXBUbXFRYmtUeW03ODh4dVluMTJCNlllZFpt?oc=5</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>finance.yahoo.com</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="inlineStr">
+        <is>
+          <t>慧與執行長：人工智慧需求“異常”，但供應鏈卻並非如此</t>
+        </is>
+      </c>
+      <c r="X11" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>SUPPLY_CHAIN_DISRUPTION</t>
+        </is>
+      </c>
+      <c r="Z11" s="4" t="inlineStr">
+        <is>
+          <t>supply chain</t>
+        </is>
+      </c>
+      <c r="AA11" s="4" t="inlineStr"/>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t>4b29cf62a8f745eab64d70327b09097b</t>
+        </is>
+      </c>
+      <c r="AC11" s="4" t="inlineStr">
+        <is>
+          <t>aa553e018d73a9b0841471ee</t>
+        </is>
+      </c>
+      <c r="AD11" s="4" t="inlineStr">
+        <is>
+          <t>6c3f7a8b41b31622b3df8dfe</t>
+        </is>
+      </c>
+      <c r="AE11" s="4" t="inlineStr"/>
+      <c r="AF11" s="4" t="inlineStr"/>
+      <c r="AG11" s="4" t="inlineStr"/>
+      <c r="AH11" s="4" t="inlineStr"/>
+      <c r="AI11" s="4" t="inlineStr"/>
+      <c r="AJ11" s="4" t="inlineStr"/>
+      <c r="AK11" s="4" t="inlineStr"/>
+      <c r="AL11" s="4" t="inlineStr"/>
+      <c r="AM11" s="4" t="inlineStr"/>
+      <c r="AN11" s="4" t="inlineStr"/>
+      <c r="AO11" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr"/>
-      <c r="AQ11" s="3" t="inlineStr"/>
-      <c r="AR11" s="3" t="inlineStr"/>
-      <c r="AS11" s="3" t="inlineStr"/>
-      <c r="AT11" s="3" t="inlineStr"/>
-      <c r="AU11" s="3" t="inlineStr"/>
-      <c r="AV11" s="3" t="inlineStr"/>
-      <c r="AW11" s="3" t="inlineStr"/>
-      <c r="AX11" s="3" t="inlineStr"/>
-      <c r="AY11" s="3" t="inlineStr"/>
-      <c r="AZ11" s="3" t="inlineStr"/>
-      <c r="BA11" s="3" t="inlineStr"/>
-      <c r="BB11" s="3" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="BC11" s="3" t="inlineStr">
+      <c r="AP11" s="4" t="inlineStr"/>
+      <c r="AQ11" s="4" t="inlineStr"/>
+      <c r="AR11" s="4" t="inlineStr"/>
+      <c r="AS11" s="4" t="inlineStr"/>
+      <c r="AT11" s="4" t="inlineStr"/>
+      <c r="AU11" s="4" t="inlineStr"/>
+      <c r="AV11" s="4" t="inlineStr"/>
+      <c r="AW11" s="4" t="inlineStr"/>
+      <c r="AX11" s="4" t="inlineStr"/>
+      <c r="AY11" s="4" t="inlineStr"/>
+      <c r="AZ11" s="4" t="inlineStr"/>
+      <c r="BA11" s="4" t="inlineStr"/>
+      <c r="BB11" s="4" t="inlineStr">
+        <is>
+          <t>HPE</t>
+        </is>
+      </c>
+      <c r="BC11" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD11" s="3" t="inlineStr"/>
-      <c r="BE11" s="3" t="inlineStr">
+      <c r="BD11" s="4" t="inlineStr"/>
+      <c r="BE11" s="4" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF11" s="3" t="inlineStr"/>
-      <c r="BG11" s="3" t="inlineStr">
+      <c r="BF11" s="4" t="inlineStr"/>
+      <c r="BG11" s="4" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH11" s="3" t="inlineStr"/>
-      <c r="BI11" s="3" t="inlineStr"/>
-      <c r="BJ11" s="3" t="inlineStr"/>
-      <c r="BK11" s="3" t="inlineStr">
+      <c r="BH11" s="4" t="inlineStr"/>
+      <c r="BI11" s="4" t="inlineStr"/>
+      <c r="BJ11" s="4" t="inlineStr"/>
+      <c r="BK11" s="4" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL11" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
+      <c r="BL11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>HPE</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Hewlett Packard Enterprise</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04T04:10:52+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>AI demand is 'exceptional,' but the supply chain is not: HPE CEO</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr"/>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04T03:49:04+08:00</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>The FTC’s Amazon Lawsuit Is Ad Tech’s History Of Opacity Repeating Itself</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>監管調查</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>'-0.717</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNQWMxNWw1aW1sYnpqcWk5ckJCZktPcF9ycnJOaTUzT2xETi1memFzVXdkMEU3a1BZQll5N01fVl9PS3duS2pMYmxpbzlrMm9xaVNxZ3ZKLTYwb3g0NWE1MTJyWXAxclFYMDhrYmQxYUVFa1Q5N1kxbE5BQy1sV2pHOEdLdndWaGh6RWJIMkpxRkJYT1hRdWlKS2tXQXJydDdjVWF0SnNpRzVoaFljeTl3?oc=5</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>AdExchanger</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>聯邦貿易委員會對亞馬遜的訴訟是廣告科技不透明的歷史重演</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY_INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>FTC</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr"/>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>8adc4fc7bfc64507a44008769d7a9d1f</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>ce51260cbab00e20c6b0b503</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr">
+        <is>
+          <t>14acfaccf29d145b81fd1796</t>
+        </is>
+      </c>
+      <c r="AE12" s="3" t="inlineStr"/>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr"/>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr"/>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr"/>
+      <c r="AM12" s="3" t="inlineStr"/>
+      <c r="AN12" s="3" t="inlineStr"/>
+      <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>0.246</t>
-        </is>
-      </c>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr"/>
-      <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="4" t="inlineStr"/>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPZnp0VmlSaS00dG1nOFlHREZRTDFNcDJwMjdvY2pTdGZPRDUtRlE5VjhzSXQwMFZfaTgwdE5xcG10TTBxejhrQ25MdXdnMFoySEpibzIxX0xPX05rNTIydFlOOUMxNmRfVkR4MWNESXBUbXFRYmtUeW03ODh4dVluMTJCNlllZFpt?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="inlineStr">
-        <is>
-          <t>finance.yahoo.com</t>
-        </is>
-      </c>
-      <c r="W12" s="4" t="inlineStr">
-        <is>
-          <t>慧與執行長：人工智慧需求“異常”，但供應鏈卻並非如此</t>
-        </is>
-      </c>
-      <c r="X12" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y12" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z12" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="inlineStr"/>
-      <c r="AC12" s="4" t="inlineStr">
-        <is>
-          <t>aa553e018d73a9b0841471ee</t>
-        </is>
-      </c>
-      <c r="AD12" s="4" t="inlineStr">
-        <is>
-          <t>6c3f7a8b41b31622b3df8dfe</t>
-        </is>
-      </c>
-      <c r="AE12" s="4" t="inlineStr"/>
-      <c r="AF12" s="4" t="inlineStr"/>
-      <c r="AG12" s="4" t="inlineStr"/>
-      <c r="AH12" s="4" t="inlineStr"/>
-      <c r="AI12" s="4" t="inlineStr"/>
-      <c r="AJ12" s="4" t="inlineStr"/>
-      <c r="AK12" s="4" t="inlineStr"/>
-      <c r="AL12" s="4" t="inlineStr"/>
-      <c r="AM12" s="4" t="inlineStr"/>
-      <c r="AN12" s="4" t="inlineStr"/>
-      <c r="AO12" s="4" t="inlineStr"/>
-      <c r="AP12" s="4" t="inlineStr"/>
-      <c r="AQ12" s="4" t="inlineStr"/>
-      <c r="AR12" s="4" t="inlineStr"/>
-      <c r="AS12" s="4" t="inlineStr"/>
-      <c r="AT12" s="4" t="inlineStr"/>
-      <c r="AU12" s="4" t="inlineStr"/>
-      <c r="AV12" s="4" t="inlineStr"/>
-      <c r="AW12" s="4" t="inlineStr"/>
-      <c r="AX12" s="4" t="inlineStr"/>
-      <c r="AY12" s="4" t="inlineStr"/>
-      <c r="AZ12" s="4" t="inlineStr"/>
-      <c r="BA12" s="4" t="inlineStr"/>
-      <c r="BB12" s="4" t="inlineStr">
-        <is>
-          <t>HPE</t>
-        </is>
-      </c>
-      <c r="BC12" s="4" t="inlineStr">
+      <c r="AP12" s="3" t="inlineStr"/>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr"/>
+      <c r="AS12" s="3" t="inlineStr"/>
+      <c r="AT12" s="3" t="inlineStr"/>
+      <c r="AU12" s="3" t="inlineStr"/>
+      <c r="AV12" s="3" t="inlineStr"/>
+      <c r="AW12" s="3" t="inlineStr"/>
+      <c r="AX12" s="3" t="inlineStr"/>
+      <c r="AY12" s="3" t="inlineStr"/>
+      <c r="AZ12" s="3" t="inlineStr"/>
+      <c r="BA12" s="3" t="inlineStr"/>
+      <c r="BB12" s="3" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="BC12" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD12" s="4" t="inlineStr"/>
-      <c r="BE12" s="4" t="inlineStr">
+      <c r="BD12" s="3" t="inlineStr"/>
+      <c r="BE12" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF12" s="4" t="inlineStr"/>
-      <c r="BG12" s="4" t="inlineStr">
+      <c r="BF12" s="3" t="inlineStr"/>
+      <c r="BG12" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH12" s="4" t="inlineStr"/>
-      <c r="BI12" s="4" t="inlineStr"/>
-      <c r="BJ12" s="4" t="inlineStr"/>
-      <c r="BK12" s="4" t="inlineStr"/>
-      <c r="BL12" s="4" t="inlineStr"/>
+      <c r="BH12" s="3" t="inlineStr"/>
+      <c r="BI12" s="3" t="inlineStr"/>
+      <c r="BJ12" s="3" t="inlineStr"/>
+      <c r="BK12" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -14234,22 +14474,22 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Regeneron Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04T03:49:04+08:00</t>
+          <t>2026-09-04T03:15:00+08:00</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>The FTC’s Amazon Lawsuit Is Ad Tech’s History Of Opacity Repeating Itself</t>
+          <t>REGN ALERT: Hagens Berman Alerts Regeneron Pharmaceuticals, Inc. (REGN) Investors to Pending Securities Fraud Class Action Amid Disclosures About Key Trial's Protocol and Ultimate Failure</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -14260,7 +14500,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>監管調查</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -14290,7 +14530,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>'-0.717</t>
+          <t>'-0.905</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr"/>
@@ -14304,17 +14544,17 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNQWMxNWw1aW1sYnpqcWk5ckJCZktPcF9ycnJOaTUzT2xETi1memFzVXdkMEU3a1BZQll5N01fVl9PS3duS2pMYmxpbzlrMm9xaVNxZ3ZKLTYwb3g0NWE1MTJyWXAxclFYMDhrYmQxYUVFa1Q5N1kxbE5BQy1sV2pHOEdLdndWaGh6RWJIMkpxRkJYT1hRdWlKS2tXQXJydDdjVWF0SnNpRzVoaFljeTl3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AJBVV95cUxPelV1OEFrNUNoeGJ4MUhoRXlheDNDVzlfV0Zjc0VWX3hBT2xMNDJ1TWVwTVczVF84MElXeFVmRjdIWXVJQjZfVjBWMmJ2Tlpyb0oycFZtc3djR3kwTGV6MnRrVGhwR05GTzlZb2dYUUtLOVpVbFhESzZsVFNrQkVycXhPMXJTRTV6d0FFQlVwUkxoVUVJRFo1cVIwRzVUZk9FUmRkTWJESlpYWFQ1TzhldlBUZXpGU3BwTk1BQVpxZ2dwWk8yM2k2eDRtclVDWWttbHY2YTNobHpKOGhuVExVbGRjcmw5ajFKNmhqVkNqNklraXBkTC04UG5TZklvTW1fMF85cXlrZUZUSVFUQ2sxRFdlNVhNVlZFQlZieDZkVS14aFhaWEY3Q0RPbTFKYTRVSXJDam12cGViX2RwaDFWTXVmMG5yOC1VQ3lpdzNJb2hSMzB6ZXluSQ?oc=5</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t>AdExchanger</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>聯邦貿易委員會對亞馬遜的訴訟是廣告科技不透明的歷史重演</t>
+          <t>REGN 警報：哈根斯伯曼 (Hagens Berman) 提醒 Regeneron Pharmaceuticals, Inc. (REGN) 投資者註意未決的證券欺詐集體訴訟，其中披露了有關關鍵試驗的協議和最終失敗的信息</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
@@ -14324,28 +14564,28 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_INVESTIGATION</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t>FTC</t>
+          <t>class action</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr"/>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>8adc4fc7bfc64507a44008769d7a9d1f</t>
+          <t>c64575696d714e089def67eb4b44ad4e</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>ce51260cbab00e20c6b0b503</t>
+          <t>38791a157c0f3be01e03c9fa</t>
         </is>
       </c>
       <c r="AD13" s="3" t="inlineStr">
         <is>
-          <t>14acfaccf29d145b81fd1796</t>
+          <t>8cd5d0104f7177725ae04d1b</t>
         </is>
       </c>
       <c r="AE13" s="3" t="inlineStr"/>
@@ -14370,14 +14610,18 @@
       <c r="AT13" s="3" t="inlineStr"/>
       <c r="AU13" s="3" t="inlineStr"/>
       <c r="AV13" s="3" t="inlineStr"/>
-      <c r="AW13" s="3" t="inlineStr"/>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
       <c r="AX13" s="3" t="inlineStr"/>
       <c r="AY13" s="3" t="inlineStr"/>
       <c r="AZ13" s="3" t="inlineStr"/>
       <c r="BA13" s="3" t="inlineStr"/>
       <c r="BB13" s="3" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="BC13" s="3" t="inlineStr">
@@ -14388,13 +14632,17 @@
       <c r="BD13" s="3" t="inlineStr"/>
       <c r="BE13" s="3" t="inlineStr">
         <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF13" s="3" t="inlineStr"/>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
       <c r="BG13" s="3" t="inlineStr">
         <is>
-          <t>公司清單／交易所參照</t>
+          <t>交易所目前名單</t>
         </is>
       </c>
       <c r="BH13" s="3" t="inlineStr"/>
@@ -14424,22 +14672,22 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals, Inc.</t>
+          <t>GoDaddy Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04T03:15:00+08:00</t>
+          <t>2026-09-04T02:05:49+08:00</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>REGN ALERT: Hagens Berman Alerts Regeneron Pharmaceuticals, Inc. (REGN) Investors to Pending Securities Fraud Class Action Amid Disclosures About Key Trial's Protocol and Ultimate Failure</t>
+          <t>GDDY SHAREHOLDER ALERT: Bronstein, Gewirtz and Grossman, LLC Announces that GoDaddy Inc. Stockholders with Substantial Losses Have Opportunity to Lead Class Action Lawsuit!</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -14480,7 +14728,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>'-0.905</t>
+          <t>'-0.705</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr"/>
@@ -14494,17 +14742,17 @@
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AJBVV95cUxPelV1OEFrNUNoeGJ4MUhoRXlheDNDVzlfV0Zjc0VWX3hBT2xMNDJ1TWVwTVczVF84MElXeFVmRjdIWXVJQjZfVjBWMmJ2Tlpyb0oycFZtc3djR3kwTGV6MnRrVGhwR05GTzlZb2dYUUtLOVpVbFhESzZsVFNrQkVycXhPMXJTRTV6d0FFQlVwUkxoVUVJRFo1cVIwRzVUZk9FUmRkTWJESlpYWFQ1TzhldlBUZXpGU3BwTk1BQVpxZ2dwWk8yM2k2eDRtclVDWWttbHY2YTNobHpKOGhuVExVbGRjcmw5ajFKNmhqVkNqNklraXBkTC04UG5TZklvTW1fMF85cXlrZUZUSVFUQ2sxRFdlNVhNVlZFQlZieDZkVS14aFhaWEY3Q0RPbTFKYTRVSXJDam12cGViX2RwaDFWTXVmMG5yOC1VQ3lpdzNJb2hSMzB6ZXluSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNSDZGalBMR0Y0SmFsalJIRnMxenFsdWQ1VmJwZWxtc3hBWVNoaGozOEFLel9SRmZyNmlQNlJraS1aSVAyT2dJLVpjbFlKOHE3RkVoYzVOb0tqd08wMUxFdUtzczZ3NHU5aEt1NllJY1VwNFE2aUUtVjNCWWZzU1B0SEdmbkwzX1RlN3QycXJ0VE9vTGxxUTJtUHotdHptQVp1bVdndjFOR1paOXEwT2lKZnNYOElXWXN0SG1wc0JtdjhMRld4SkJYQUgyZGMyS05BbE1iYmFMRnhDQmZkV2RRajJLTWo?oc=5</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>ACCESS Newswire</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>REGN 警報：哈根斯伯曼 (Hagens Berman) 提醒 Regeneron Pharmaceuticals, Inc. (REGN) 投資者註意未決的證券欺詐集體訴訟，其中披露了有關關鍵試驗的協議和最終失敗的信息</t>
+          <t>GDDY 股東提醒：Bronstein、Gewirtz 和 Grossman, LLC 宣布遭受重大損失的 GoDaddy Inc. 股東有機會提起集體訴訟！</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
@@ -14525,17 +14773,17 @@
       <c r="AA14" s="3" t="inlineStr"/>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>c64575696d714e089def67eb4b44ad4e</t>
+          <t>e36ac9f0dc79428a8bb2961b98bea6cb</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>38791a157c0f3be01e03c9fa</t>
+          <t>495f965b81435c5aec023a8d</t>
         </is>
       </c>
       <c r="AD14" s="3" t="inlineStr">
         <is>
-          <t>8cd5d0104f7177725ae04d1b</t>
+          <t>bd43b6190fadea4fa33334e2</t>
         </is>
       </c>
       <c r="AE14" s="3" t="inlineStr"/>
@@ -14562,7 +14810,7 @@
       <c r="AV14" s="3" t="inlineStr"/>
       <c r="AW14" s="3" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>NYSE</t>
         </is>
       </c>
       <c r="AX14" s="3" t="inlineStr"/>
@@ -14571,7 +14819,7 @@
       <c r="BA14" s="3" t="inlineStr"/>
       <c r="BB14" s="3" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="BC14" s="3" t="inlineStr">
@@ -14582,12 +14830,12 @@
       <c r="BD14" s="3" t="inlineStr"/>
       <c r="BE14" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
       <c r="BF14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
       <c r="BG14" s="3" t="inlineStr">
@@ -14610,751 +14858,395 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>GDDY</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>GoDaddy Inc. Class A Common Stock</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04T02:05:49+08:00</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>GDDY SHAREHOLDER ALERT: Bronstein, Gewirtz and Grossman, LLC Announces that GoDaddy Inc. Stockholders with Substantial Losses Have Opportunity to Lead Class Action Lawsuit!</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>BSX</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Boston Scientific Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04T00:16:27+08:00</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Boston Scientific (BSX) Issues Multiple Worldwide Product Recalls</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>產品召回</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>'-0.705</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr"/>
-      <c r="T15" s="3" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>0.042</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr"/>
+      <c r="Q15" s="4" t="inlineStr"/>
+      <c r="R15" s="4" t="inlineStr"/>
+      <c r="S15" s="4" t="inlineStr"/>
+      <c r="T15" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U15" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNSDZGalBMR0Y0SmFsalJIRnMxenFsdWQ1VmJwZWxtc3hBWVNoaGozOEFLel9SRmZyNmlQNlJraS1aSVAyT2dJLVpjbFlKOHE3RkVoYzVOb0tqd08wMUxFdUtzczZ3NHU5aEt1NllJY1VwNFE2aUUtVjNCWWZzU1B0SEdmbkwzX1RlN3QycXJ0VE9vTGxxUTJtUHotdHptQVp1bVdndjFOR1paOXEwT2lKZnNYOElXWXN0SG1wc0JtdjhMRld4SkJYQUgyZGMyS05BbE1iYmFMRnhDQmZkV2RRajJLTWo?oc=5</t>
-        </is>
-      </c>
-      <c r="V15" s="3" t="inlineStr">
-        <is>
-          <t>ACCESS Newswire</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="inlineStr">
-        <is>
-          <t>GDDY 股東提醒：Bronstein、Gewirtz 和 Grossman, LLC 宣布遭受重大損失的 GoDaddy Inc. 股東有機會提起集體訴訟！</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z15" s="3" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA15" s="3" t="inlineStr"/>
-      <c r="AB15" s="3" t="inlineStr">
-        <is>
-          <t>e36ac9f0dc79428a8bb2961b98bea6cb</t>
-        </is>
-      </c>
-      <c r="AC15" s="3" t="inlineStr">
-        <is>
-          <t>495f965b81435c5aec023a8d</t>
-        </is>
-      </c>
-      <c r="AD15" s="3" t="inlineStr">
-        <is>
-          <t>bd43b6190fadea4fa33334e2</t>
-        </is>
-      </c>
-      <c r="AE15" s="3" t="inlineStr"/>
-      <c r="AF15" s="3" t="inlineStr"/>
-      <c r="AG15" s="3" t="inlineStr"/>
-      <c r="AH15" s="3" t="inlineStr"/>
-      <c r="AI15" s="3" t="inlineStr"/>
-      <c r="AJ15" s="3" t="inlineStr"/>
-      <c r="AK15" s="3" t="inlineStr"/>
-      <c r="AL15" s="3" t="inlineStr"/>
-      <c r="AM15" s="3" t="inlineStr"/>
-      <c r="AN15" s="3" t="inlineStr"/>
-      <c r="AO15" s="3" t="inlineStr">
+      <c r="U15" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxONWc5MzhsakRxR1ZrOEQxZDFPQ1lhVXBmYjBha0VsZi00Y05PMnZkbFN3NUc4UEJvYnVOa1JubnZtMTIyNUhOMlJjM2Vmb3ppV3RDVU1DUlU4S0pZbnUtWmNCd296c25GZXdiT2Mzc3hzVjE2SnU2Q3RWUjlaNXdoRzVnd3hBVm5STGU5ekx4SWxNNTV5RmpvYlFpQjRveVU?oc=5</t>
+        </is>
+      </c>
+      <c r="V15" s="4" t="inlineStr">
+        <is>
+          <t>finance.yahoo.com</t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="inlineStr">
+        <is>
+          <t>波士頓科學公司 (BSX) 在全球召回多項產品</t>
+        </is>
+      </c>
+      <c r="X15" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y15" s="4" t="inlineStr">
+        <is>
+          <t>PRODUCT_RECALL</t>
+        </is>
+      </c>
+      <c r="Z15" s="4" t="inlineStr">
+        <is>
+          <t>product recall</t>
+        </is>
+      </c>
+      <c r="AA15" s="4" t="inlineStr"/>
+      <c r="AB15" s="4" t="inlineStr">
+        <is>
+          <t>95d008d6c03f444a82c3f94ddd3b5aab</t>
+        </is>
+      </c>
+      <c r="AC15" s="4" t="inlineStr">
+        <is>
+          <t>55985b65cf2ed55e27be34dd</t>
+        </is>
+      </c>
+      <c r="AD15" s="4" t="inlineStr">
+        <is>
+          <t>e85678c7fd1d879d8f5ce35d</t>
+        </is>
+      </c>
+      <c r="AE15" s="4" t="inlineStr"/>
+      <c r="AF15" s="4" t="inlineStr"/>
+      <c r="AG15" s="4" t="inlineStr"/>
+      <c r="AH15" s="4" t="inlineStr"/>
+      <c r="AI15" s="4" t="inlineStr"/>
+      <c r="AJ15" s="4" t="inlineStr"/>
+      <c r="AK15" s="4" t="inlineStr"/>
+      <c r="AL15" s="4" t="inlineStr"/>
+      <c r="AM15" s="4" t="inlineStr"/>
+      <c r="AN15" s="4" t="inlineStr"/>
+      <c r="AO15" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr"/>
-      <c r="AQ15" s="3" t="inlineStr"/>
-      <c r="AR15" s="3" t="inlineStr"/>
-      <c r="AS15" s="3" t="inlineStr"/>
-      <c r="AT15" s="3" t="inlineStr"/>
-      <c r="AU15" s="3" t="inlineStr"/>
-      <c r="AV15" s="3" t="inlineStr"/>
-      <c r="AW15" s="3" t="inlineStr">
+      <c r="AP15" s="4" t="inlineStr"/>
+      <c r="AQ15" s="4" t="inlineStr"/>
+      <c r="AR15" s="4" t="inlineStr"/>
+      <c r="AS15" s="4" t="inlineStr"/>
+      <c r="AT15" s="4" t="inlineStr"/>
+      <c r="AU15" s="4" t="inlineStr"/>
+      <c r="AV15" s="4" t="inlineStr"/>
+      <c r="AW15" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX15" s="3" t="inlineStr"/>
-      <c r="AY15" s="3" t="inlineStr"/>
-      <c r="AZ15" s="3" t="inlineStr"/>
-      <c r="BA15" s="3" t="inlineStr"/>
-      <c r="BB15" s="3" t="inlineStr">
-        <is>
-          <t>GDDY</t>
-        </is>
-      </c>
-      <c r="BC15" s="3" t="inlineStr">
+      <c r="AX15" s="4" t="inlineStr"/>
+      <c r="AY15" s="4" t="inlineStr"/>
+      <c r="AZ15" s="4" t="inlineStr"/>
+      <c r="BA15" s="4" t="inlineStr"/>
+      <c r="BB15" s="4" t="inlineStr">
+        <is>
+          <t>BSX</t>
+        </is>
+      </c>
+      <c r="BC15" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD15" s="3" t="inlineStr"/>
-      <c r="BE15" s="3" t="inlineStr">
+      <c r="BD15" s="4" t="inlineStr"/>
+      <c r="BE15" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF15" s="3" t="inlineStr">
+      <c r="BF15" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG15" s="3" t="inlineStr">
+      <c r="BG15" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH15" s="3" t="inlineStr"/>
-      <c r="BI15" s="3" t="inlineStr"/>
-      <c r="BJ15" s="3" t="inlineStr"/>
-      <c r="BK15" s="3" t="inlineStr">
+      <c r="BH15" s="4" t="inlineStr"/>
+      <c r="BI15" s="4" t="inlineStr"/>
+      <c r="BJ15" s="4" t="inlineStr"/>
+      <c r="BK15" s="4" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL15" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
+      <c r="BL15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Uber Technologies, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04T01:02:00+08:00</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>I was laid off from Uber again. As a boomerang employee, my worst fear came true.</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr"/>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Pentair</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04T00:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Bronstein, Gewirtz &amp; Grossman LLC Urges Pentair plc Investors to Act: Class Action Filed Alleging Investor Harm</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>'-0.724</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAJBVV95cUxOMzJUY0o3dnZHbk9JVzNOdE1oTVRyZUE2U2tyQXFIVjU4WkdDb3BlQmJZNXcyNEF1S0dyU2VRYVBJME5ocVZobHhDOUFHVXZwTnQtdFN0RWpDdmU4NkxRV3MxNE5iWExxWkdpRGFmdDlpN0M0QmFHdlJjMjJ1elpGMkJCYXdrMmZzNm9TZzg2WHVxVEthdmVtRklyQVI2Q3RRS2t0SFZoSXBpTzFjcjBfM1loc1BZR2VEN1RWLTRHUTdjcHByd0dZYl9CVGdvYVdYYmNjYU00eFZjLXQ5MkpnSjBYUXk0RWFrVVg3ZUlRbm9LekR0QWlqMHpGc19kQkktaVpoYlZ3S3pPT0l4dmNVTEw1WGlxV3k3TmxaVGgtZE1GdjY3cWM3ZHBwaHg?oc=5</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>WBOC TV</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>Bronstein, Gewirtz &amp; Grossman LLC 敦促 Pentair plc 投資者採取行動：提起集體訴訟，指控投資者受到傷害</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr"/>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>8c7ea643782d42ccb39ea121ee8457e3</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>904795eb1543f2f78e0c2287</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr">
+        <is>
+          <t>bd70771ee4d2251c91648496</t>
+        </is>
+      </c>
+      <c r="AE16" s="3" t="inlineStr"/>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr"/>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr"/>
+      <c r="AM16" s="3" t="inlineStr"/>
+      <c r="AN16" s="3" t="inlineStr"/>
+      <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O16" s="4" t="inlineStr">
-        <is>
-          <t>'-0.762</t>
-        </is>
-      </c>
-      <c r="P16" s="4" t="inlineStr"/>
-      <c r="Q16" s="4" t="inlineStr"/>
-      <c r="R16" s="4" t="inlineStr"/>
-      <c r="S16" s="4" t="inlineStr"/>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQV1lSRXpvTW9FUm9jVkw4XzZOS0ZBYndfR0VlUVE1eTBXVHYtUjI0aVgtYWNHQ3o0eEtaR0c5Tnl6T0lJYjNYUkpKbXk2RG5MeXdvaS0yRXNpWC1VVk1lVDVpRkoxb25xVHRfeGRCdUVMb2l1cHNPZ1kwVjF6SEVqU2R6RGlyRnBzTTdCYQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="inlineStr">
-        <is>
-          <t>Business Insider</t>
-        </is>
-      </c>
-      <c r="W16" s="4" t="inlineStr">
-        <is>
-          <t>我又被 Uber 解雇了。身為迴力鏢員工，我最擔心的事情成真了。</t>
-        </is>
-      </c>
-      <c r="X16" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y16" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z16" s="4" t="inlineStr">
-        <is>
-          <t>laid off</t>
-        </is>
-      </c>
-      <c r="AA16" s="4" t="inlineStr"/>
-      <c r="AB16" s="4" t="inlineStr"/>
-      <c r="AC16" s="4" t="inlineStr">
-        <is>
-          <t>a767a2e2968e7ba2894a38b9</t>
-        </is>
-      </c>
-      <c r="AD16" s="4" t="inlineStr">
-        <is>
-          <t>9a3859e34af691eaf36ef1aa</t>
-        </is>
-      </c>
-      <c r="AE16" s="4" t="inlineStr"/>
-      <c r="AF16" s="4" t="inlineStr"/>
-      <c r="AG16" s="4" t="inlineStr"/>
-      <c r="AH16" s="4" t="inlineStr"/>
-      <c r="AI16" s="4" t="inlineStr"/>
-      <c r="AJ16" s="4" t="inlineStr"/>
-      <c r="AK16" s="4" t="inlineStr"/>
-      <c r="AL16" s="4" t="inlineStr"/>
-      <c r="AM16" s="4" t="inlineStr"/>
-      <c r="AN16" s="4" t="inlineStr"/>
-      <c r="AO16" s="4" t="inlineStr"/>
-      <c r="AP16" s="4" t="inlineStr"/>
-      <c r="AQ16" s="4" t="inlineStr"/>
-      <c r="AR16" s="4" t="inlineStr"/>
-      <c r="AS16" s="4" t="inlineStr"/>
-      <c r="AT16" s="4" t="inlineStr"/>
-      <c r="AU16" s="4" t="inlineStr"/>
-      <c r="AV16" s="4" t="inlineStr"/>
-      <c r="AW16" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX16" s="4" t="inlineStr"/>
-      <c r="AY16" s="4" t="inlineStr"/>
-      <c r="AZ16" s="4" t="inlineStr"/>
-      <c r="BA16" s="4" t="inlineStr"/>
-      <c r="BB16" s="4" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="BC16" s="4" t="inlineStr">
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr"/>
+      <c r="AS16" s="3" t="inlineStr"/>
+      <c r="AT16" s="3" t="inlineStr"/>
+      <c r="AU16" s="3" t="inlineStr"/>
+      <c r="AV16" s="3" t="inlineStr"/>
+      <c r="AW16" s="3" t="inlineStr"/>
+      <c r="AX16" s="3" t="inlineStr"/>
+      <c r="AY16" s="3" t="inlineStr"/>
+      <c r="AZ16" s="3" t="inlineStr"/>
+      <c r="BA16" s="3" t="inlineStr"/>
+      <c r="BB16" s="3" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="BC16" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD16" s="4" t="inlineStr"/>
-      <c r="BE16" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF16" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG16" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH16" s="4" t="inlineStr"/>
-      <c r="BI16" s="4" t="inlineStr"/>
-      <c r="BJ16" s="4" t="inlineStr"/>
-      <c r="BK16" s="4" t="inlineStr"/>
-      <c r="BL16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>BSX</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Boston Scientific Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04T00:16:27+08:00</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Boston Scientific (BSX) Issues Multiple Worldwide Product Recalls</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>產品召回</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr"/>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O17" s="4" t="inlineStr">
-        <is>
-          <t>0.042</t>
-        </is>
-      </c>
-      <c r="P17" s="4" t="inlineStr"/>
-      <c r="Q17" s="4" t="inlineStr"/>
-      <c r="R17" s="4" t="inlineStr"/>
-      <c r="S17" s="4" t="inlineStr"/>
-      <c r="T17" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U17" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxONWc5MzhsakRxR1ZrOEQxZDFPQ1lhVXBmYjBha0VsZi00Y05PMnZkbFN3NUc4UEJvYnVOa1JubnZtMTIyNUhOMlJjM2Vmb3ppV3RDVU1DUlU4S0pZbnUtWmNCd296c25GZXdiT2Mzc3hzVjE2SnU2Q3RWUjlaNXdoRzVnd3hBVm5STGU5ekx4SWxNNTV5RmpvYlFpQjRveVU?oc=5</t>
-        </is>
-      </c>
-      <c r="V17" s="4" t="inlineStr">
-        <is>
-          <t>finance.yahoo.com</t>
-        </is>
-      </c>
-      <c r="W17" s="4" t="inlineStr">
-        <is>
-          <t>波士頓科學公司 (BSX) 在全球召回多項產品</t>
-        </is>
-      </c>
-      <c r="X17" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y17" s="4" t="inlineStr">
-        <is>
-          <t>PRODUCT_RECALL</t>
-        </is>
-      </c>
-      <c r="Z17" s="4" t="inlineStr">
-        <is>
-          <t>product recall</t>
-        </is>
-      </c>
-      <c r="AA17" s="4" t="inlineStr"/>
-      <c r="AB17" s="4" t="inlineStr"/>
-      <c r="AC17" s="4" t="inlineStr">
-        <is>
-          <t>55985b65cf2ed55e27be34dd</t>
-        </is>
-      </c>
-      <c r="AD17" s="4" t="inlineStr">
-        <is>
-          <t>e85678c7fd1d879d8f5ce35d</t>
-        </is>
-      </c>
-      <c r="AE17" s="4" t="inlineStr"/>
-      <c r="AF17" s="4" t="inlineStr"/>
-      <c r="AG17" s="4" t="inlineStr"/>
-      <c r="AH17" s="4" t="inlineStr"/>
-      <c r="AI17" s="4" t="inlineStr"/>
-      <c r="AJ17" s="4" t="inlineStr"/>
-      <c r="AK17" s="4" t="inlineStr"/>
-      <c r="AL17" s="4" t="inlineStr"/>
-      <c r="AM17" s="4" t="inlineStr"/>
-      <c r="AN17" s="4" t="inlineStr"/>
-      <c r="AO17" s="4" t="inlineStr"/>
-      <c r="AP17" s="4" t="inlineStr"/>
-      <c r="AQ17" s="4" t="inlineStr"/>
-      <c r="AR17" s="4" t="inlineStr"/>
-      <c r="AS17" s="4" t="inlineStr"/>
-      <c r="AT17" s="4" t="inlineStr"/>
-      <c r="AU17" s="4" t="inlineStr"/>
-      <c r="AV17" s="4" t="inlineStr"/>
-      <c r="AW17" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX17" s="4" t="inlineStr"/>
-      <c r="AY17" s="4" t="inlineStr"/>
-      <c r="AZ17" s="4" t="inlineStr"/>
-      <c r="BA17" s="4" t="inlineStr"/>
-      <c r="BB17" s="4" t="inlineStr">
-        <is>
-          <t>BSX</t>
-        </is>
-      </c>
-      <c r="BC17" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD17" s="4" t="inlineStr"/>
-      <c r="BE17" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF17" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG17" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH17" s="4" t="inlineStr"/>
-      <c r="BI17" s="4" t="inlineStr"/>
-      <c r="BJ17" s="4" t="inlineStr"/>
-      <c r="BK17" s="4" t="inlineStr"/>
-      <c r="BL17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Pentair</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04T00:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Bronstein, Gewirtz &amp; Grossman LLC Urges Pentair plc Investors to Act: Class Action Filed Alleging Investor Harm</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>'-0.724</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="3" t="inlineStr"/>
-      <c r="R18" s="3" t="inlineStr"/>
-      <c r="S18" s="3" t="inlineStr"/>
-      <c r="T18" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U18" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirAJBVV95cUxOMzJUY0o3dnZHbk9JVzNOdE1oTVRyZUE2U2tyQXFIVjU4WkdDb3BlQmJZNXcyNEF1S0dyU2VRYVBJME5ocVZobHhDOUFHVXZwTnQtdFN0RWpDdmU4NkxRV3MxNE5iWExxWkdpRGFmdDlpN0M0QmFHdlJjMjJ1elpGMkJCYXdrMmZzNm9TZzg2WHVxVEthdmVtRklyQVI2Q3RRS2t0SFZoSXBpTzFjcjBfM1loc1BZR2VEN1RWLTRHUTdjcHByd0dZYl9CVGdvYVdYYmNjYU00eFZjLXQ5MkpnSjBYUXk0RWFrVVg3ZUlRbm9LekR0QWlqMHpGc19kQkktaVpoYlZ3S3pPT0l4dmNVTEw1WGlxV3k3TmxaVGgtZE1GdjY3cWM3ZHBwaHg?oc=5</t>
-        </is>
-      </c>
-      <c r="V18" s="3" t="inlineStr">
-        <is>
-          <t>WBOC TV</t>
-        </is>
-      </c>
-      <c r="W18" s="3" t="inlineStr">
-        <is>
-          <t>Bronstein, Gewirtz &amp; Grossman LLC 敦促 Pentair plc 投資者採取行動：提起集體訴訟，指控投資者受到傷害</t>
-        </is>
-      </c>
-      <c r="X18" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z18" s="3" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA18" s="3" t="inlineStr"/>
-      <c r="AB18" s="3" t="inlineStr">
-        <is>
-          <t>8c7ea643782d42ccb39ea121ee8457e3</t>
-        </is>
-      </c>
-      <c r="AC18" s="3" t="inlineStr">
-        <is>
-          <t>904795eb1543f2f78e0c2287</t>
-        </is>
-      </c>
-      <c r="AD18" s="3" t="inlineStr">
-        <is>
-          <t>bd70771ee4d2251c91648496</t>
-        </is>
-      </c>
-      <c r="AE18" s="3" t="inlineStr"/>
-      <c r="AF18" s="3" t="inlineStr"/>
-      <c r="AG18" s="3" t="inlineStr"/>
-      <c r="AH18" s="3" t="inlineStr"/>
-      <c r="AI18" s="3" t="inlineStr"/>
-      <c r="AJ18" s="3" t="inlineStr"/>
-      <c r="AK18" s="3" t="inlineStr"/>
-      <c r="AL18" s="3" t="inlineStr"/>
-      <c r="AM18" s="3" t="inlineStr"/>
-      <c r="AN18" s="3" t="inlineStr"/>
-      <c r="AO18" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP18" s="3" t="inlineStr"/>
-      <c r="AQ18" s="3" t="inlineStr"/>
-      <c r="AR18" s="3" t="inlineStr"/>
-      <c r="AS18" s="3" t="inlineStr"/>
-      <c r="AT18" s="3" t="inlineStr"/>
-      <c r="AU18" s="3" t="inlineStr"/>
-      <c r="AV18" s="3" t="inlineStr"/>
-      <c r="AW18" s="3" t="inlineStr"/>
-      <c r="AX18" s="3" t="inlineStr"/>
-      <c r="AY18" s="3" t="inlineStr"/>
-      <c r="AZ18" s="3" t="inlineStr"/>
-      <c r="BA18" s="3" t="inlineStr"/>
-      <c r="BB18" s="3" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="BC18" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD18" s="3" t="inlineStr"/>
-      <c r="BE18" s="3" t="inlineStr">
+      <c r="BD16" s="3" t="inlineStr"/>
+      <c r="BE16" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF18" s="3" t="inlineStr"/>
-      <c r="BG18" s="3" t="inlineStr">
+      <c r="BF16" s="3" t="inlineStr"/>
+      <c r="BG16" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH18" s="3" t="inlineStr"/>
-      <c r="BI18" s="3" t="inlineStr"/>
-      <c r="BJ18" s="3" t="inlineStr"/>
-      <c r="BK18" s="3" t="inlineStr">
+      <c r="BH16" s="3" t="inlineStr"/>
+      <c r="BI16" s="3" t="inlineStr"/>
+      <c r="BJ16" s="3" t="inlineStr"/>
+      <c r="BK16" s="3" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL18" s="3" t="inlineStr">
+      <c r="BL16" s="3" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL18"/>
+  <autoFilter ref="A1:BL16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-09-04.xlsx
+++ b/news_daily/2026-09-04.xlsx
@@ -888,28 +888,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -953,7 +957,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -962,7 +966,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>8b35308336804450a5dc843c786f2fe6</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>32523e2ca6db3212131116f9</t>
@@ -983,7 +991,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1019,10 +1031,22 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1058,28 +1082,32 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1123,7 +1151,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -1132,7 +1160,11 @@
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>8bbf8b667b894d7ab83ff7d8ad2ea213</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>d7c55f9d61d54404dd49de5b</t>
@@ -1153,7 +1185,11 @@
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="2" t="inlineStr"/>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
@@ -1197,10 +1233,22 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1236,28 +1284,32 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1301,7 +1353,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -1310,7 +1362,11 @@
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>a9e9fae1b3304b66ba90bda38dde111c</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>06a5f6be3670bf832ffa67de</t>
@@ -1331,7 +1387,11 @@
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr"/>
@@ -1375,10 +1435,22 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
-      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -3366,28 +3438,32 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3431,7 +3507,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -3440,7 +3516,11 @@
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr"/>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>3b737a1819b64542a7e6f21df45bbd85</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
           <t>27abc4ed7633d1d98b9b7ca1</t>
@@ -3461,7 +3541,11 @@
       <c r="AL15" s="2" t="inlineStr"/>
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr"/>
-      <c r="AO15" s="2" t="inlineStr"/>
+      <c r="AO15" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP15" s="2" t="inlineStr"/>
       <c r="AQ15" s="2" t="inlineStr"/>
       <c r="AR15" s="2" t="inlineStr"/>
@@ -3497,10 +3581,22 @@
         </is>
       </c>
       <c r="BH15" s="2" t="inlineStr"/>
-      <c r="BI15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ15" s="2" t="inlineStr"/>
-      <c r="BK15" s="2" t="inlineStr"/>
-      <c r="BL15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3536,28 +3632,32 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3601,7 +3701,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -3610,7 +3710,11 @@
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr"/>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>221824592f434ba6a002c30fbd6acc9d</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
           <t>3e5d541c50edaa45fe63ad6f</t>
@@ -3631,7 +3735,11 @@
       <c r="AL16" s="2" t="inlineStr"/>
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr"/>
-      <c r="AO16" s="2" t="inlineStr"/>
+      <c r="AO16" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP16" s="2" t="inlineStr"/>
       <c r="AQ16" s="2" t="inlineStr"/>
       <c r="AR16" s="2" t="inlineStr"/>
@@ -3675,10 +3783,22 @@
         </is>
       </c>
       <c r="BH16" s="2" t="inlineStr"/>
-      <c r="BI16" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ16" s="2" t="inlineStr"/>
-      <c r="BK16" s="2" t="inlineStr"/>
-      <c r="BL16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3916,28 +4036,32 @@
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -3981,7 +4105,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -3990,7 +4114,11 @@
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr"/>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>c4d56abbcbf045d2b751d141f34259d5</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
           <t>8d84f3b37e1e1a3fadcefcf7</t>
@@ -4011,7 +4139,11 @@
       <c r="AL18" s="2" t="inlineStr"/>
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr"/>
-      <c r="AO18" s="2" t="inlineStr"/>
+      <c r="AO18" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP18" s="2" t="inlineStr"/>
       <c r="AQ18" s="2" t="inlineStr"/>
       <c r="AR18" s="2" t="inlineStr"/>
@@ -4055,10 +4187,22 @@
         </is>
       </c>
       <c r="BH18" s="2" t="inlineStr"/>
-      <c r="BI18" s="2" t="inlineStr"/>
+      <c r="BI18" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ18" s="2" t="inlineStr"/>
-      <c r="BK18" s="2" t="inlineStr"/>
-      <c r="BL18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -4292,28 +4436,32 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4357,7 +4505,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -4366,7 +4514,11 @@
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr"/>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>11b8488de3904e429f89bf9572927de3</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
           <t>3a2d2202b456e14f6dccc833</t>
@@ -4387,7 +4539,11 @@
       <c r="AL20" s="2" t="inlineStr"/>
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr"/>
-      <c r="AO20" s="2" t="inlineStr"/>
+      <c r="AO20" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP20" s="2" t="inlineStr"/>
       <c r="AQ20" s="2" t="inlineStr"/>
       <c r="AR20" s="2" t="inlineStr"/>
@@ -4423,10 +4579,22 @@
         </is>
       </c>
       <c r="BH20" s="2" t="inlineStr"/>
-      <c r="BI20" s="2" t="inlineStr"/>
+      <c r="BI20" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ20" s="2" t="inlineStr"/>
-      <c r="BK20" s="2" t="inlineStr"/>
-      <c r="BL20" s="2" t="inlineStr"/>
+      <c r="BK20" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4462,28 +4630,32 @@
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -4527,7 +4699,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -4536,7 +4708,11 @@
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr"/>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>5b50a1df788c45788c88991522b661d5</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
           <t>b41874ecd67d57c6268585ff</t>
@@ -4557,7 +4733,11 @@
       <c r="AL21" s="2" t="inlineStr"/>
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr"/>
-      <c r="AO21" s="2" t="inlineStr"/>
+      <c r="AO21" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP21" s="2" t="inlineStr"/>
       <c r="AQ21" s="2" t="inlineStr"/>
       <c r="AR21" s="2" t="inlineStr"/>
@@ -4601,10 +4781,22 @@
         </is>
       </c>
       <c r="BH21" s="2" t="inlineStr"/>
-      <c r="BI21" s="2" t="inlineStr"/>
+      <c r="BI21" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ21" s="2" t="inlineStr"/>
-      <c r="BK21" s="2" t="inlineStr"/>
-      <c r="BL21" s="2" t="inlineStr"/>
+      <c r="BK21" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4640,28 +4832,32 @@
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4705,7 +4901,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -4714,7 +4910,11 @@
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr"/>
-      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>af19edabd5df44c4bc283ed2a887a6f3</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
           <t>8208070e755edb4af8031fb8</t>
@@ -4735,7 +4935,11 @@
       <c r="AL22" s="2" t="inlineStr"/>
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr"/>
-      <c r="AO22" s="2" t="inlineStr"/>
+      <c r="AO22" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP22" s="2" t="inlineStr"/>
       <c r="AQ22" s="2" t="inlineStr"/>
       <c r="AR22" s="2" t="inlineStr"/>
@@ -4779,10 +4983,22 @@
         </is>
       </c>
       <c r="BH22" s="2" t="inlineStr"/>
-      <c r="BI22" s="2" t="inlineStr"/>
+      <c r="BI22" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ22" s="2" t="inlineStr"/>
-      <c r="BK22" s="2" t="inlineStr"/>
-      <c r="BL22" s="2" t="inlineStr"/>
+      <c r="BK22" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -5222,28 +5438,32 @@
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -5287,7 +5507,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -5296,7 +5516,11 @@
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr"/>
-      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>e8d9fcc58b7b44e19183fe8942d1b0b4</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
           <t>512903384e0f9cec08769de2</t>
@@ -5317,7 +5541,11 @@
       <c r="AL25" s="2" t="inlineStr"/>
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr"/>
-      <c r="AO25" s="2" t="inlineStr"/>
+      <c r="AO25" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP25" s="2" t="inlineStr"/>
       <c r="AQ25" s="2" t="inlineStr"/>
       <c r="AR25" s="2" t="inlineStr"/>
@@ -5353,10 +5581,22 @@
         </is>
       </c>
       <c r="BH25" s="2" t="inlineStr"/>
-      <c r="BI25" s="2" t="inlineStr"/>
+      <c r="BI25" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ25" s="2" t="inlineStr"/>
-      <c r="BK25" s="2" t="inlineStr"/>
-      <c r="BL25" s="2" t="inlineStr"/>
+      <c r="BK25" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5392,28 +5632,32 @@
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -5457,7 +5701,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -5466,7 +5710,11 @@
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr"/>
-      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>91981ca3e87f469295b083a6a5a9fdb9</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
           <t>0f313b9d44289f4991e9f311</t>
@@ -5487,7 +5735,11 @@
       <c r="AL26" s="2" t="inlineStr"/>
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr"/>
-      <c r="AO26" s="2" t="inlineStr"/>
+      <c r="AO26" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP26" s="2" t="inlineStr"/>
       <c r="AQ26" s="2" t="inlineStr"/>
       <c r="AR26" s="2" t="inlineStr"/>
@@ -5531,10 +5783,22 @@
         </is>
       </c>
       <c r="BH26" s="2" t="inlineStr"/>
-      <c r="BI26" s="2" t="inlineStr"/>
+      <c r="BI26" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ26" s="2" t="inlineStr"/>
-      <c r="BK26" s="2" t="inlineStr"/>
-      <c r="BL26" s="2" t="inlineStr"/>
+      <c r="BK26" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5585,13 +5849,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -5644,7 +5912,11 @@
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr"/>
-      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>509866d255684e7abd7309dffe5979f0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
           <t>1fb4118c6ebe2678bc22eb9e</t>
@@ -5665,7 +5937,11 @@
       <c r="AL27" s="2" t="inlineStr"/>
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr"/>
-      <c r="AO27" s="2" t="inlineStr"/>
+      <c r="AO27" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP27" s="2" t="inlineStr"/>
       <c r="AQ27" s="2" t="inlineStr"/>
       <c r="AR27" s="2" t="inlineStr"/>
@@ -5711,8 +5987,16 @@
       <c r="BH27" s="2" t="inlineStr"/>
       <c r="BI27" s="2" t="inlineStr"/>
       <c r="BJ27" s="2" t="inlineStr"/>
-      <c r="BK27" s="2" t="inlineStr"/>
-      <c r="BL27" s="2" t="inlineStr"/>
+      <c r="BK27" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5748,28 +6032,32 @@
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -5813,7 +6101,7 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -5822,7 +6110,11 @@
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr"/>
-      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>fdb33c5d279c4376a7fcf6f8e4f3e654</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
           <t>570ad67730495ecd464aee1b</t>
@@ -5843,7 +6135,11 @@
       <c r="AL28" s="2" t="inlineStr"/>
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr"/>
-      <c r="AO28" s="2" t="inlineStr"/>
+      <c r="AO28" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP28" s="2" t="inlineStr"/>
       <c r="AQ28" s="2" t="inlineStr"/>
       <c r="AR28" s="2" t="inlineStr"/>
@@ -5887,10 +6183,22 @@
         </is>
       </c>
       <c r="BH28" s="2" t="inlineStr"/>
-      <c r="BI28" s="2" t="inlineStr"/>
+      <c r="BI28" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ28" s="2" t="inlineStr"/>
-      <c r="BK28" s="2" t="inlineStr"/>
-      <c r="BL28" s="2" t="inlineStr"/>
+      <c r="BK28" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6128,28 +6436,32 @@
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -6193,7 +6505,7 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -6202,7 +6514,11 @@
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr"/>
-      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>92faee990af147eb8994a96fadc999f4</t>
+        </is>
+      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
           <t>c0e5a37af98a2cd13a91dd6a</t>
@@ -6223,7 +6539,11 @@
       <c r="AL30" s="2" t="inlineStr"/>
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr"/>
-      <c r="AO30" s="2" t="inlineStr"/>
+      <c r="AO30" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP30" s="2" t="inlineStr"/>
       <c r="AQ30" s="2" t="inlineStr"/>
       <c r="AR30" s="2" t="inlineStr"/>
@@ -6267,10 +6587,22 @@
         </is>
       </c>
       <c r="BH30" s="2" t="inlineStr"/>
-      <c r="BI30" s="2" t="inlineStr"/>
+      <c r="BI30" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ30" s="2" t="inlineStr"/>
-      <c r="BK30" s="2" t="inlineStr"/>
-      <c r="BL30" s="2" t="inlineStr"/>
+      <c r="BK30" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -6496,28 +6828,32 @@
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -6561,7 +6897,7 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -6570,7 +6906,11 @@
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr"/>
-      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>6354b00f208e43dabd78bc455771b440</t>
+        </is>
+      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
           <t>d4ccd50ddb9def3c9b2754a8</t>
@@ -6591,7 +6931,11 @@
       <c r="AL32" s="2" t="inlineStr"/>
       <c r="AM32" s="2" t="inlineStr"/>
       <c r="AN32" s="2" t="inlineStr"/>
-      <c r="AO32" s="2" t="inlineStr"/>
+      <c r="AO32" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP32" s="2" t="inlineStr"/>
       <c r="AQ32" s="2" t="inlineStr"/>
       <c r="AR32" s="2" t="inlineStr"/>
@@ -6635,10 +6979,22 @@
         </is>
       </c>
       <c r="BH32" s="2" t="inlineStr"/>
-      <c r="BI32" s="2" t="inlineStr"/>
+      <c r="BI32" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ32" s="2" t="inlineStr"/>
-      <c r="BK32" s="2" t="inlineStr"/>
-      <c r="BL32" s="2" t="inlineStr"/>
+      <c r="BK32" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6674,28 +7030,32 @@
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -6739,7 +7099,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -6748,7 +7108,11 @@
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr"/>
-      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>a5db3e75735b448286c0a22f6f6b99f8</t>
+        </is>
+      </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
           <t>afff75ab69dca90bdc1ccad1</t>
@@ -6769,7 +7133,11 @@
       <c r="AL33" s="2" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr"/>
       <c r="AN33" s="2" t="inlineStr"/>
-      <c r="AO33" s="2" t="inlineStr"/>
+      <c r="AO33" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP33" s="2" t="inlineStr"/>
       <c r="AQ33" s="2" t="inlineStr"/>
       <c r="AR33" s="2" t="inlineStr"/>
@@ -6813,10 +7181,22 @@
         </is>
       </c>
       <c r="BH33" s="2" t="inlineStr"/>
-      <c r="BI33" s="2" t="inlineStr"/>
+      <c r="BI33" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ33" s="2" t="inlineStr"/>
-      <c r="BK33" s="2" t="inlineStr"/>
-      <c r="BL33" s="2" t="inlineStr"/>
+      <c r="BK33" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6852,28 +7232,32 @@
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -6917,7 +7301,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -6926,7 +7310,11 @@
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr"/>
-      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>03aeb8df37d9408c8ba0551b8ababbe6</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
           <t>479a1f5d5f852d6f1bcadd56</t>
@@ -6947,7 +7335,11 @@
       <c r="AL34" s="2" t="inlineStr"/>
       <c r="AM34" s="2" t="inlineStr"/>
       <c r="AN34" s="2" t="inlineStr"/>
-      <c r="AO34" s="2" t="inlineStr"/>
+      <c r="AO34" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP34" s="2" t="inlineStr"/>
       <c r="AQ34" s="2" t="inlineStr"/>
       <c r="AR34" s="2" t="inlineStr"/>
@@ -6991,10 +7383,22 @@
         </is>
       </c>
       <c r="BH34" s="2" t="inlineStr"/>
-      <c r="BI34" s="2" t="inlineStr"/>
+      <c r="BI34" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ34" s="2" t="inlineStr"/>
-      <c r="BK34" s="2" t="inlineStr"/>
-      <c r="BL34" s="2" t="inlineStr"/>
+      <c r="BK34" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7434,28 +7838,32 @@
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -7499,7 +7907,7 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -7508,7 +7916,11 @@
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr"/>
-      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>c6775fa889e741ffa17d7674e21a0c16</t>
+        </is>
+      </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
           <t>e43f9ce0ecf6421318d74fa6</t>
@@ -7529,7 +7941,11 @@
       <c r="AL37" s="2" t="inlineStr"/>
       <c r="AM37" s="2" t="inlineStr"/>
       <c r="AN37" s="2" t="inlineStr"/>
-      <c r="AO37" s="2" t="inlineStr"/>
+      <c r="AO37" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP37" s="2" t="inlineStr"/>
       <c r="AQ37" s="2" t="inlineStr"/>
       <c r="AR37" s="2" t="inlineStr"/>
@@ -7573,10 +7989,22 @@
         </is>
       </c>
       <c r="BH37" s="2" t="inlineStr"/>
-      <c r="BI37" s="2" t="inlineStr"/>
+      <c r="BI37" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ37" s="2" t="inlineStr"/>
-      <c r="BK37" s="2" t="inlineStr"/>
-      <c r="BL37" s="2" t="inlineStr"/>
+      <c r="BK37" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -8388,28 +8816,32 @@
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -8453,7 +8885,7 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -8462,7 +8894,11 @@
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr"/>
-      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>f802b92e76044f2aa2f1751435baad39</t>
+        </is>
+      </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
           <t>814f35b7c7668e53d5e41bac</t>
@@ -8483,7 +8919,11 @@
       <c r="AL42" s="2" t="inlineStr"/>
       <c r="AM42" s="2" t="inlineStr"/>
       <c r="AN42" s="2" t="inlineStr"/>
-      <c r="AO42" s="2" t="inlineStr"/>
+      <c r="AO42" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP42" s="2" t="inlineStr"/>
       <c r="AQ42" s="2" t="inlineStr"/>
       <c r="AR42" s="2" t="inlineStr"/>
@@ -8519,10 +8959,22 @@
         </is>
       </c>
       <c r="BH42" s="2" t="inlineStr"/>
-      <c r="BI42" s="2" t="inlineStr"/>
+      <c r="BI42" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ42" s="2" t="inlineStr"/>
-      <c r="BK42" s="2" t="inlineStr"/>
-      <c r="BL42" s="2" t="inlineStr"/>
+      <c r="BK42" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -8756,28 +9208,32 @@
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -8821,7 +9277,7 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -8830,7 +9286,11 @@
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr"/>
-      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>57fa477390db46e3b1b0df186966e488</t>
+        </is>
+      </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
           <t>3d91e3723e5c3a2258c0cf7f</t>
@@ -8851,7 +9311,11 @@
       <c r="AL44" s="2" t="inlineStr"/>
       <c r="AM44" s="2" t="inlineStr"/>
       <c r="AN44" s="2" t="inlineStr"/>
-      <c r="AO44" s="2" t="inlineStr"/>
+      <c r="AO44" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP44" s="2" t="inlineStr"/>
       <c r="AQ44" s="2" t="inlineStr"/>
       <c r="AR44" s="2" t="inlineStr"/>
@@ -8895,10 +9359,22 @@
         </is>
       </c>
       <c r="BH44" s="2" t="inlineStr"/>
-      <c r="BI44" s="2" t="inlineStr"/>
+      <c r="BI44" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ44" s="2" t="inlineStr"/>
-      <c r="BK44" s="2" t="inlineStr"/>
-      <c r="BL44" s="2" t="inlineStr"/>
+      <c r="BK44" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8934,28 +9410,32 @@
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -8999,7 +9479,7 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -9008,7 +9488,11 @@
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr"/>
-      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>b627ff4fec6243a6980263beb8e50d78</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
           <t>2231a03fca9993c3f0ef7700</t>
@@ -9029,7 +9513,11 @@
       <c r="AL45" s="2" t="inlineStr"/>
       <c r="AM45" s="2" t="inlineStr"/>
       <c r="AN45" s="2" t="inlineStr"/>
-      <c r="AO45" s="2" t="inlineStr"/>
+      <c r="AO45" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP45" s="2" t="inlineStr"/>
       <c r="AQ45" s="2" t="inlineStr"/>
       <c r="AR45" s="2" t="inlineStr"/>
@@ -9073,10 +9561,22 @@
         </is>
       </c>
       <c r="BH45" s="2" t="inlineStr"/>
-      <c r="BI45" s="2" t="inlineStr"/>
+      <c r="BI45" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ45" s="2" t="inlineStr"/>
-      <c r="BK45" s="2" t="inlineStr"/>
-      <c r="BL45" s="2" t="inlineStr"/>
+      <c r="BK45" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9112,28 +9612,32 @@
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -9177,7 +9681,7 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -9186,7 +9690,11 @@
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr"/>
-      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>d6177b772dfe44f1991bffa081c0377f</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
           <t>abb0f12546b8b64d16ef64e4</t>
@@ -9207,7 +9715,11 @@
       <c r="AL46" s="2" t="inlineStr"/>
       <c r="AM46" s="2" t="inlineStr"/>
       <c r="AN46" s="2" t="inlineStr"/>
-      <c r="AO46" s="2" t="inlineStr"/>
+      <c r="AO46" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP46" s="2" t="inlineStr"/>
       <c r="AQ46" s="2" t="inlineStr"/>
       <c r="AR46" s="2" t="inlineStr"/>
@@ -9251,10 +9763,22 @@
         </is>
       </c>
       <c r="BH46" s="2" t="inlineStr"/>
-      <c r="BI46" s="2" t="inlineStr"/>
+      <c r="BI46" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ46" s="2" t="inlineStr"/>
-      <c r="BK46" s="2" t="inlineStr"/>
-      <c r="BL46" s="2" t="inlineStr"/>
+      <c r="BK46" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -9884,28 +10408,32 @@
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -9949,7 +10477,7 @@
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -9958,7 +10486,11 @@
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr"/>
-      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>3318dcca82534c0c8308cf30e0f3adde</t>
+        </is>
+      </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
           <t>46a7593fb5dfa278a3e805b3</t>
@@ -9979,7 +10511,11 @@
       <c r="AL50" s="2" t="inlineStr"/>
       <c r="AM50" s="2" t="inlineStr"/>
       <c r="AN50" s="2" t="inlineStr"/>
-      <c r="AO50" s="2" t="inlineStr"/>
+      <c r="AO50" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP50" s="2" t="inlineStr"/>
       <c r="AQ50" s="2" t="inlineStr"/>
       <c r="AR50" s="2" t="inlineStr"/>
@@ -10023,10 +10559,22 @@
         </is>
       </c>
       <c r="BH50" s="2" t="inlineStr"/>
-      <c r="BI50" s="2" t="inlineStr"/>
+      <c r="BI50" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ50" s="2" t="inlineStr"/>
-      <c r="BK50" s="2" t="inlineStr"/>
-      <c r="BL50" s="2" t="inlineStr"/>
+      <c r="BK50" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -10668,28 +11216,32 @@
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -10733,7 +11285,7 @@
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -10742,7 +11294,11 @@
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr"/>
-      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>bf4572254a014ff8bc85846bf18f4ae5</t>
+        </is>
+      </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
           <t>8f589acb9a786a18dab6f655</t>
@@ -10763,7 +11319,11 @@
       <c r="AL54" s="2" t="inlineStr"/>
       <c r="AM54" s="2" t="inlineStr"/>
       <c r="AN54" s="2" t="inlineStr"/>
-      <c r="AO54" s="2" t="inlineStr"/>
+      <c r="AO54" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP54" s="2" t="inlineStr"/>
       <c r="AQ54" s="2" t="inlineStr"/>
       <c r="AR54" s="2" t="inlineStr"/>
@@ -10807,10 +11367,22 @@
         </is>
       </c>
       <c r="BH54" s="2" t="inlineStr"/>
-      <c r="BI54" s="2" t="inlineStr"/>
+      <c r="BI54" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ54" s="2" t="inlineStr"/>
-      <c r="BK54" s="2" t="inlineStr"/>
-      <c r="BL54" s="2" t="inlineStr"/>
+      <c r="BK54" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10861,13 +11433,17 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -10920,7 +11496,11 @@
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr"/>
-      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>739d971c9de24b0b84efeb20d3cdf3e8</t>
+        </is>
+      </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
           <t>9d5fb652deae1e9b85b49c76</t>
@@ -10941,7 +11521,11 @@
       <c r="AL55" s="2" t="inlineStr"/>
       <c r="AM55" s="2" t="inlineStr"/>
       <c r="AN55" s="2" t="inlineStr"/>
-      <c r="AO55" s="2" t="inlineStr"/>
+      <c r="AO55" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP55" s="2" t="inlineStr"/>
       <c r="AQ55" s="2" t="inlineStr"/>
       <c r="AR55" s="2" t="inlineStr"/>
@@ -10987,8 +11571,16 @@
       <c r="BH55" s="2" t="inlineStr"/>
       <c r="BI55" s="2" t="inlineStr"/>
       <c r="BJ55" s="2" t="inlineStr"/>
-      <c r="BK55" s="2" t="inlineStr"/>
-      <c r="BL55" s="2" t="inlineStr"/>
+      <c r="BK55" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -11424,28 +12016,32 @@
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -11489,7 +12085,7 @@
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -11498,7 +12094,11 @@
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr"/>
-      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>20a8ef6c72d441e7800e1ecf7bd04ba1</t>
+        </is>
+      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
           <t>f557d9ef1e9f2e30fcaae0b3</t>
@@ -11519,7 +12119,11 @@
       <c r="AL58" s="2" t="inlineStr"/>
       <c r="AM58" s="2" t="inlineStr"/>
       <c r="AN58" s="2" t="inlineStr"/>
-      <c r="AO58" s="2" t="inlineStr"/>
+      <c r="AO58" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP58" s="2" t="inlineStr"/>
       <c r="AQ58" s="2" t="inlineStr"/>
       <c r="AR58" s="2" t="inlineStr"/>
@@ -11563,10 +12167,22 @@
         </is>
       </c>
       <c r="BH58" s="2" t="inlineStr"/>
-      <c r="BI58" s="2" t="inlineStr"/>
+      <c r="BI58" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ58" s="2" t="inlineStr"/>
-      <c r="BK58" s="2" t="inlineStr"/>
-      <c r="BL58" s="2" t="inlineStr"/>
+      <c r="BK58" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11602,28 +12218,32 @@
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -11667,7 +12287,7 @@
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -11676,7 +12296,11 @@
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr"/>
-      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>a4181e1d1a264a738ccf7383c498b1db</t>
+        </is>
+      </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
           <t>6abd7819f7c36bb4d6647e22</t>
@@ -11697,7 +12321,11 @@
       <c r="AL59" s="2" t="inlineStr"/>
       <c r="AM59" s="2" t="inlineStr"/>
       <c r="AN59" s="2" t="inlineStr"/>
-      <c r="AO59" s="2" t="inlineStr"/>
+      <c r="AO59" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP59" s="2" t="inlineStr"/>
       <c r="AQ59" s="2" t="inlineStr"/>
       <c r="AR59" s="2" t="inlineStr"/>
@@ -11741,10 +12369,22 @@
         </is>
       </c>
       <c r="BH59" s="2" t="inlineStr"/>
-      <c r="BI59" s="2" t="inlineStr"/>
+      <c r="BI59" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ59" s="2" t="inlineStr"/>
-      <c r="BK59" s="2" t="inlineStr"/>
-      <c r="BL59" s="2" t="inlineStr"/>
+      <c r="BK59" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
